--- a/results_fedavg_dirichlet_4class/round_metrics.xlsx
+++ b/results_fedavg_dirichlet_4class/round_metrics.xlsx
@@ -480,28 +480,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9339622641509434</v>
+        <v>0.9528301886792452</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2224773545837346</v>
+        <v>0.2162557588714473</v>
       </c>
       <c r="D2" t="n">
-        <v>0.89375</v>
+        <v>0.91875</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8930856372032843</v>
+        <v>0.9184712987519148</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8930856372032843</v>
+        <v>0.9184712987519148</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8984571469865587</v>
+        <v>0.9196725522590524</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8937499999999999</v>
+        <v>0.91875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9888541666666666</v>
+        <v>0.9863541666666666</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +509,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9622641509433962</v>
+        <v>0.9716981132075472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.134227546599676</v>
+        <v>0.1358794208334864</v>
       </c>
       <c r="D3" t="n">
-        <v>0.89375</v>
+        <v>0.9125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8926803560347143</v>
+        <v>0.9120996055539692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8926803560347143</v>
+        <v>0.9120996055539694</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9020555095023181</v>
+        <v>0.9141994523092084</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8937499999999999</v>
+        <v>0.9125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9875520833333332</v>
+        <v>0.99109375</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +538,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9622641509433962</v>
+        <v>0.9905660377358492</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1236667164056649</v>
+        <v>0.0884990535483185</v>
       </c>
       <c r="D4" t="n">
-        <v>0.89375</v>
+        <v>0.875</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8924346851978431</v>
+        <v>0.8741719281204469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8924346851978431</v>
+        <v>0.8741719281204468</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9026199494949496</v>
+        <v>0.8881458966565349</v>
       </c>
       <c r="H4" t="n">
-        <v>0.89375</v>
+        <v>0.875</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9885416666666668</v>
+        <v>0.9921875</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +567,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9716981132075472</v>
+        <v>0.9622641509433962</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0933536640983426</v>
+        <v>0.0889897025981039</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>0.89375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8994003879294267</v>
+        <v>0.8930869544879755</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8994003879294267</v>
+        <v>0.8930869544879755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.903391472868217</v>
+        <v>0.8977566999339781</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.89375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9890104166666668</v>
+        <v>0.9922395833333334</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +596,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.981132075471698</v>
+        <v>0.9716981132075472</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06565762699564109</v>
+        <v>0.0692112987008789</v>
       </c>
       <c r="D6" t="n">
-        <v>0.925</v>
+        <v>0.91875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9245663581351934</v>
+        <v>0.9184003015177004</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9245663581351934</v>
+        <v>0.9184003015177004</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9293080393916276</v>
+        <v>0.921619166741118</v>
       </c>
       <c r="H6" t="n">
-        <v>0.925</v>
+        <v>0.91875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9896875000000001</v>
+        <v>0.9941666666666666</v>
       </c>
     </row>
   </sheetData>
